--- a/12600415.xlsx
+++ b/12600415.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDCA6903-DB39-42A6-8F52-D4228FB7F330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F79CCA0-CCA1-4BD0-B491-649162E5CF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -216,7 +216,16 @@
     <t>Learned Baisc Syntaxes of OOPS.</t>
   </si>
   <si>
-    <t>Leanring constructor in oops using cpp.</t>
+    <t>Learning constructor in oops using cpp.</t>
+  </si>
+  <si>
+    <t>Learned Basic Syntaxes of SQL</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>Learned Some more syntaxes of SQL.</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1063,7 @@
         <v>60</v>
       </c>
       <c r="D7" s="14">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="E7" s="14">
         <v>30</v>
@@ -1066,15 +1075,15 @@
         <v>300</v>
       </c>
       <c r="H7" s="14">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>53</v>
@@ -1091,7 +1100,7 @@
     </row>
     <row r="8" spans="1:14" ht="30.75">
       <c r="A8" s="13">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B8" s="14">
         <v>450</v>
@@ -1100,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="14">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="E8" s="14">
         <v>10</v>
@@ -1112,7 +1121,7 @@
         <v>200</v>
       </c>
       <c r="H8" s="14">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" ref="I8" si="2">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
@@ -1135,49 +1144,97 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="15">
+      <c r="A9" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>60</v>
+      </c>
+      <c r="E9" s="14">
+        <v>10</v>
+      </c>
+      <c r="F9" s="14">
+        <v>350</v>
+      </c>
+      <c r="G9" s="14">
+        <v>350</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="30.75">
+      <c r="A10" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>240</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>15</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="shared" ref="I10" si="4">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
+        <v>735</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" ref="J10" si="5">IF(I10="","",1440-I10)</f>
+        <v>705</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="13"/>
@@ -2487,11 +2544,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2509,11 +2566,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2531,11 +2588,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2553,11 +2610,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2575,11 +2632,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2597,11 +2654,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2619,11 +2676,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2641,11 +2698,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2663,11 +2720,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2685,11 +2742,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2707,11 +2764,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2729,11 +2786,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2751,11 +2808,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2773,11 +2830,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2795,11 +2852,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -2817,11 +2874,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -2839,11 +2896,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -2861,11 +2918,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -2883,11 +2940,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -2905,11 +2962,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -2927,11 +2984,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -2949,11 +3006,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -2971,11 +3028,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -2993,11 +3050,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3015,11 +3072,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3037,11 +3094,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3059,11 +3116,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3081,11 +3138,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3103,11 +3160,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3125,11 +3182,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3147,11 +3204,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3169,11 +3226,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3191,11 +3248,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3213,11 +3270,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3235,11 +3292,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3257,11 +3314,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3279,11 +3336,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3301,11 +3358,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3323,11 +3380,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3345,11 +3402,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3367,11 +3424,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3389,11 +3446,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3411,11 +3468,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3433,11 +3490,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3455,11 +3512,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3477,11 +3534,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3499,11 +3556,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3521,11 +3578,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3543,11 +3600,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3565,11 +3622,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3587,11 +3644,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3609,11 +3666,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3631,11 +3688,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3653,11 +3710,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3675,11 +3732,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3697,11 +3754,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3719,11 +3776,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3741,11 +3798,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3763,11 +3820,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3785,11 +3842,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -3807,11 +3864,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -3829,11 +3886,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -3851,11 +3908,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -3873,11 +3930,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -3895,11 +3952,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -3917,11 +3974,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -3939,11 +3996,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -3961,11 +4018,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -3983,11 +4040,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4005,11 +4062,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4027,11 +4084,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4049,11 +4106,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4071,11 +4128,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4093,11 +4150,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4115,11 +4172,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4137,11 +4194,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4159,11 +4216,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4181,11 +4238,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4203,11 +4260,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4225,11 +4282,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4247,11 +4304,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4269,11 +4326,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4291,11 +4348,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4313,11 +4370,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4335,11 +4392,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4357,11 +4414,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4379,11 +4436,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4401,11 +4458,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4423,11 +4480,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4445,11 +4502,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4467,11 +4524,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4489,11 +4546,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4511,11 +4568,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4533,11 +4590,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4555,11 +4612,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4577,11 +4634,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4599,11 +4656,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4621,11 +4678,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4643,11 +4700,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4665,11 +4722,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4687,11 +4744,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4709,11 +4766,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4731,11 +4788,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4753,11 +4810,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4775,11 +4832,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4797,11 +4854,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -4819,11 +4876,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -4841,11 +4898,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -4863,11 +4920,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -4885,11 +4942,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -4907,11 +4964,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -4929,11 +4986,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -4951,11 +5008,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -4973,11 +5030,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -4995,11 +5052,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5017,11 +5074,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5039,11 +5096,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5061,11 +5118,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5083,11 +5140,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5105,11 +5162,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5127,11 +5184,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5149,11 +5206,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5171,11 +5228,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5193,11 +5250,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5215,11 +5272,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5237,11 +5294,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5259,11 +5316,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5281,11 +5338,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5303,11 +5360,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5325,11 +5382,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5347,11 +5404,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5369,11 +5426,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5391,11 +5448,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5413,11 +5470,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5435,11 +5492,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5457,11 +5514,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5479,11 +5536,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5501,11 +5558,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5523,11 +5580,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5545,11 +5602,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5567,11 +5624,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5589,11 +5646,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5611,11 +5668,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5633,11 +5690,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5655,11 +5712,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5677,11 +5734,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5699,11 +5756,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5721,11 +5778,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5743,11 +5800,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5765,11 +5822,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5787,11 +5844,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -5809,11 +5866,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -5831,11 +5888,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -5853,11 +5910,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -5875,11 +5932,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -5897,11 +5954,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -5919,11 +5976,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -5941,11 +5998,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -5963,11 +6020,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -5985,11 +6042,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6007,11 +6064,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6029,11 +6086,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6051,11 +6108,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6073,11 +6130,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6095,11 +6152,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6117,11 +6174,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6139,11 +6196,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6161,11 +6218,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6183,11 +6240,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6205,11 +6262,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6227,11 +6284,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6249,11 +6306,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6271,11 +6328,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6293,11 +6350,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6315,11 +6372,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6337,11 +6394,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6359,11 +6416,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6381,11 +6438,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6403,11 +6460,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6425,11 +6482,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6447,11 +6504,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6469,11 +6526,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6491,11 +6548,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6513,11 +6570,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6535,11 +6592,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6557,11 +6614,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6579,11 +6636,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6601,11 +6658,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6623,11 +6680,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6645,11 +6702,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6667,11 +6724,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6689,11 +6746,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6711,11 +6768,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6733,11 +6790,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6755,11 +6812,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6777,11 +6834,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6799,11 +6856,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -6821,11 +6878,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -6843,11 +6900,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -6865,11 +6922,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -6887,11 +6944,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -6909,11 +6966,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -6931,11 +6988,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -6953,11 +7010,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -6975,11 +7032,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -6997,11 +7054,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7019,11 +7076,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7041,11 +7098,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7063,11 +7120,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7085,11 +7142,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7107,11 +7164,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7129,11 +7186,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7151,11 +7208,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7173,11 +7230,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7195,11 +7252,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7217,11 +7274,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7239,11 +7296,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7261,11 +7318,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7283,11 +7340,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7305,11 +7362,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7327,11 +7384,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7349,11 +7406,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7371,11 +7428,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7393,11 +7450,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7415,11 +7472,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7437,11 +7494,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7459,11 +7516,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7481,11 +7538,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7503,11 +7560,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7525,11 +7582,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7547,11 +7604,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7569,11 +7626,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7591,11 +7648,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7613,11 +7670,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7635,11 +7692,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7657,11 +7714,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7679,11 +7736,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7701,11 +7758,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7723,11 +7780,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7745,11 +7802,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7767,11 +7824,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7789,11 +7846,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -7811,11 +7868,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -7833,11 +7890,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -7855,11 +7912,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -7877,11 +7934,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -7899,11 +7956,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -7921,11 +7978,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -7943,11 +8000,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -7965,11 +8022,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -7987,11 +8044,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8009,11 +8066,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8031,11 +8088,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8053,11 +8110,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8075,11 +8132,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8097,11 +8154,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8119,11 +8176,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8141,11 +8198,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8163,11 +8220,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8185,11 +8242,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8207,11 +8264,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8229,11 +8286,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8251,11 +8308,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8273,11 +8330,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8295,11 +8352,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8317,11 +8374,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8339,11 +8396,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8361,11 +8418,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8383,11 +8440,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8405,11 +8462,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8427,11 +8484,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8449,11 +8506,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8471,11 +8528,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8493,11 +8550,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8515,11 +8572,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8537,11 +8594,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8559,11 +8616,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8581,11 +8638,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8603,11 +8660,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8625,11 +8682,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8647,11 +8704,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8669,11 +8726,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8691,11 +8748,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8713,11 +8770,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8735,11 +8792,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8757,11 +8814,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8779,11 +8836,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -8801,11 +8858,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -8823,11 +8880,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -8845,11 +8902,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -8867,11 +8924,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -8889,11 +8946,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -8911,11 +8968,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -8933,11 +8990,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -8955,11 +9012,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -8977,11 +9034,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -8999,11 +9056,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9021,11 +9078,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9043,11 +9100,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9065,11 +9122,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9087,11 +9144,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9109,11 +9166,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9131,11 +9188,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9153,11 +9210,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9175,11 +9232,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9197,11 +9254,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9219,11 +9276,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9241,11 +9298,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9263,11 +9320,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9285,11 +9342,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9307,11 +9364,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9329,11 +9386,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9351,11 +9408,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9373,11 +9430,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9395,11 +9452,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9417,11 +9474,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9439,11 +9496,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9461,11 +9518,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9483,11 +9540,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9505,11 +9562,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9527,11 +9584,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I453" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I453" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J453" si="15">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J453" si="17">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9549,11 +9606,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9571,11 +9628,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9593,11 +9650,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9615,11 +9672,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9637,11 +9694,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9659,11 +9716,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9681,11 +9738,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9703,11 +9760,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9725,11 +9782,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9747,11 +9804,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9769,11 +9826,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12600415.xlsx
+++ b/12600415.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F79CCA0-CCA1-4BD0-B491-649162E5CF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A51FF187-AC32-4571-9A66-296446F5086A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,15 @@
   </si>
   <si>
     <t>Learned Some more syntaxes of SQL.</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Did some coding practice of python and cpp.</t>
+  </si>
+  <si>
+    <t>Revised DBMS chapter 1.</t>
   </si>
 </sst>
 </file>
@@ -1236,49 +1245,97 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+    <row r="11" spans="1:14" ht="30.75">
+      <c r="A11" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B11" s="14">
+        <v>400</v>
+      </c>
+      <c r="C11" s="14">
+        <v>10</v>
+      </c>
+      <c r="D11" s="14">
+        <v>40</v>
+      </c>
+      <c r="E11" s="14">
+        <v>20</v>
+      </c>
+      <c r="F11" s="14">
+        <v>400</v>
+      </c>
+      <c r="G11" s="14">
+        <v>400</v>
+      </c>
+      <c r="H11" s="14">
+        <v>60</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" ref="I11" si="6">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
+        <v>930</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" ref="J11" si="7">IF(I11="","",1440-I11)</f>
+        <v>510</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15">
+      <c r="A12" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
+      <c r="C12" s="14">
+        <v>10</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14">
+        <v>250</v>
+      </c>
+      <c r="G12" s="14">
+        <v>250</v>
+      </c>
+      <c r="H12" s="14">
+        <v>150</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" ref="I12" si="8">IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
+        <v>1010</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" ref="J12" si="9">IF(I12="","",1440-I12)</f>
+        <v>430</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="13"/>
@@ -2544,11 +2601,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2566,11 +2623,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2588,11 +2645,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2610,11 +2667,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2632,11 +2689,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2654,11 +2711,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2676,11 +2733,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2698,11 +2755,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2720,11 +2777,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2742,11 +2799,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2764,11 +2821,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2786,11 +2843,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2808,11 +2865,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2830,11 +2887,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2852,11 +2909,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -2874,11 +2931,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -2896,11 +2953,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -2918,11 +2975,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -2940,11 +2997,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -2962,11 +3019,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -2984,11 +3041,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3006,11 +3063,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3028,11 +3085,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3050,11 +3107,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3072,11 +3129,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3094,11 +3151,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3116,11 +3173,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3138,11 +3195,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3160,11 +3217,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3182,11 +3239,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3204,11 +3261,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3226,11 +3283,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3248,11 +3305,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3270,11 +3327,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3292,11 +3349,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3314,11 +3371,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3336,11 +3393,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3358,11 +3415,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3380,11 +3437,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3402,11 +3459,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3424,11 +3481,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3446,11 +3503,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3468,11 +3525,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3490,11 +3547,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3512,11 +3569,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3534,11 +3591,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3556,11 +3613,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3578,11 +3635,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3600,11 +3657,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3622,11 +3679,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3644,11 +3701,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3666,11 +3723,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3688,11 +3745,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3710,11 +3767,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3732,11 +3789,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3754,11 +3811,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3776,11 +3833,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3798,11 +3855,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3820,11 +3877,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3842,11 +3899,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -3864,11 +3921,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -3886,11 +3943,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -3908,11 +3965,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -3930,11 +3987,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -3952,11 +4009,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -3974,11 +4031,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -3996,11 +4053,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4018,11 +4075,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4040,11 +4097,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4062,11 +4119,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4084,11 +4141,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4106,11 +4163,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4128,11 +4185,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4150,11 +4207,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4172,11 +4229,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4194,11 +4251,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4216,11 +4273,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4238,11 +4295,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4260,11 +4317,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4282,11 +4339,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4304,11 +4361,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4326,11 +4383,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4348,11 +4405,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4370,11 +4427,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4392,11 +4449,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4414,11 +4471,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4436,11 +4493,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4458,11 +4515,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4480,11 +4537,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4502,11 +4559,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4524,11 +4581,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4546,11 +4603,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4568,11 +4625,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4590,11 +4647,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4612,11 +4669,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4634,11 +4691,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4656,11 +4713,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4678,11 +4735,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4700,11 +4757,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4722,11 +4779,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4744,11 +4801,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4766,11 +4823,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4788,11 +4845,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4810,11 +4867,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4832,11 +4889,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4854,11 +4911,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -4876,11 +4933,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -4898,11 +4955,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -4920,11 +4977,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -4942,11 +4999,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -4964,11 +5021,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -4986,11 +5043,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5008,11 +5065,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5030,11 +5087,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5052,11 +5109,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5074,11 +5131,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5096,11 +5153,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5118,11 +5175,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5140,11 +5197,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5162,11 +5219,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5184,11 +5241,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5206,11 +5263,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5228,11 +5285,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5250,11 +5307,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5272,11 +5329,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5294,11 +5351,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5316,11 +5373,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5338,11 +5395,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5360,11 +5417,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5382,11 +5439,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5404,11 +5461,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5426,11 +5483,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5448,11 +5505,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5470,11 +5527,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5492,11 +5549,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5514,11 +5571,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5536,11 +5593,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5558,11 +5615,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5580,11 +5637,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5602,11 +5659,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5624,11 +5681,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5646,11 +5703,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5668,11 +5725,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5690,11 +5747,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5712,11 +5769,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5734,11 +5791,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5756,11 +5813,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5778,11 +5835,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5800,11 +5857,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5822,11 +5879,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5844,11 +5901,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -5866,11 +5923,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -5888,11 +5945,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -5910,11 +5967,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -5932,11 +5989,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -5954,11 +6011,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -5976,11 +6033,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -5998,11 +6055,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6020,11 +6077,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6042,11 +6099,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6064,11 +6121,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6086,11 +6143,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6108,11 +6165,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6130,11 +6187,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6152,11 +6209,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6174,11 +6231,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6196,11 +6253,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6218,11 +6275,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6240,11 +6297,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6262,11 +6319,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6284,11 +6341,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6306,11 +6363,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6328,11 +6385,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6350,11 +6407,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6372,11 +6429,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6394,11 +6451,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6416,11 +6473,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6438,11 +6495,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6460,11 +6517,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6482,11 +6539,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6504,11 +6561,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6526,11 +6583,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6548,11 +6605,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6570,11 +6627,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6592,11 +6649,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6614,11 +6671,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6636,11 +6693,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6658,11 +6715,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6680,11 +6737,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6702,11 +6759,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6724,11 +6781,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6746,11 +6803,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6768,11 +6825,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6790,11 +6847,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6812,11 +6869,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6834,11 +6891,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6856,11 +6913,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -6878,11 +6935,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -6900,11 +6957,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -6922,11 +6979,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -6944,11 +7001,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -6966,11 +7023,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -6988,11 +7045,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7010,11 +7067,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7032,11 +7089,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7054,11 +7111,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7076,11 +7133,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7098,11 +7155,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7120,11 +7177,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7142,11 +7199,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7164,11 +7221,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7186,11 +7243,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7208,11 +7265,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7230,11 +7287,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7252,11 +7309,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7274,11 +7331,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7296,11 +7353,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7318,11 +7375,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7340,11 +7397,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7362,11 +7419,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7384,11 +7441,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7406,11 +7463,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7428,11 +7485,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7450,11 +7507,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7472,11 +7529,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7494,11 +7551,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7516,11 +7573,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7538,11 +7595,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7560,11 +7617,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7582,11 +7639,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7604,11 +7661,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7626,11 +7683,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7648,11 +7705,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7670,11 +7727,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7692,11 +7749,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7714,11 +7771,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7736,11 +7793,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7758,11 +7815,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7780,11 +7837,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7802,11 +7859,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7824,11 +7881,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7846,11 +7903,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -7868,11 +7925,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -7890,11 +7947,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -7912,11 +7969,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -7934,11 +7991,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -7956,11 +8013,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -7978,11 +8035,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8000,11 +8057,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8022,11 +8079,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8044,11 +8101,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8066,11 +8123,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8088,11 +8145,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8110,11 +8167,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8132,11 +8189,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8154,11 +8211,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8176,11 +8233,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8198,11 +8255,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8220,11 +8277,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8242,11 +8299,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8264,11 +8321,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8286,11 +8343,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8308,11 +8365,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8330,11 +8387,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8352,11 +8409,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8374,11 +8431,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8396,11 +8453,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8418,11 +8475,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8440,11 +8497,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8462,11 +8519,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8484,11 +8541,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8506,11 +8563,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8528,11 +8585,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8550,11 +8607,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8572,11 +8629,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8594,11 +8651,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8616,11 +8673,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8638,11 +8695,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8660,11 +8717,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8682,11 +8739,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8704,11 +8761,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8726,11 +8783,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8748,11 +8805,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8770,11 +8827,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8792,11 +8849,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8814,11 +8871,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8836,11 +8893,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -8858,11 +8915,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -8880,11 +8937,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -8902,11 +8959,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -8924,11 +8981,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -8946,11 +9003,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -8968,11 +9025,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -8990,11 +9047,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9012,11 +9069,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9034,11 +9091,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9056,11 +9113,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9078,11 +9135,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9100,11 +9157,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9122,11 +9179,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9144,11 +9201,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9166,11 +9223,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9188,11 +9245,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9210,11 +9267,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9232,11 +9289,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9254,11 +9311,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9276,11 +9333,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9298,11 +9355,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9320,11 +9377,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9342,11 +9399,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9364,11 +9421,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9386,11 +9443,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9408,11 +9465,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9430,11 +9487,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9452,11 +9509,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9474,11 +9531,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9496,11 +9553,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9518,11 +9575,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9540,11 +9597,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9562,11 +9619,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9584,11 +9641,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I453" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I453" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J453" si="17">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J453" si="21">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9606,11 +9663,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9628,11 +9685,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9650,11 +9707,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9672,11 +9729,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9694,11 +9751,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9716,11 +9773,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9738,11 +9795,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9760,11 +9817,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9782,11 +9839,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9804,11 +9861,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9826,11 +9883,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12600415.xlsx
+++ b/12600415.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A51FF187-AC32-4571-9A66-296446F5086A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D44F80E2-2BA9-4481-853E-A0602D629EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,15 @@
   </si>
   <si>
     <t>Revised DBMS chapter 1.</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Revised Vocab.</t>
   </si>
 </sst>
 </file>
@@ -1337,49 +1346,97 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+    <row r="13" spans="1:14" ht="15">
+      <c r="A13" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>240</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" ref="I13" si="10">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
+        <v>750</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" ref="J13" si="11">IF(I13="","",1440-I13)</f>
+        <v>690</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15">
+      <c r="A14" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>15</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" ref="I14" si="12">IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
+        <v>675</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" ref="J14" si="13">IF(I14="","",1440-I14)</f>
+        <v>765</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13"/>
@@ -2601,11 +2658,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="14">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="15">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2623,11 +2680,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2645,11 +2702,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2667,11 +2724,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2689,11 +2746,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2711,11 +2768,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2733,11 +2790,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2755,11 +2812,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2777,11 +2834,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2799,11 +2856,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2821,11 +2878,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2843,11 +2900,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2865,11 +2922,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2887,11 +2944,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2909,11 +2966,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -2931,11 +2988,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -2953,11 +3010,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -2975,11 +3032,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -2997,11 +3054,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3019,11 +3076,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3041,11 +3098,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3063,11 +3120,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3085,11 +3142,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3107,11 +3164,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3129,11 +3186,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3151,11 +3208,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3173,11 +3230,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3195,11 +3252,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3217,11 +3274,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3239,11 +3296,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3261,11 +3318,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3283,11 +3340,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3305,11 +3362,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3327,11 +3384,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3349,11 +3406,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3371,11 +3428,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3393,11 +3450,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3415,11 +3472,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3437,11 +3494,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3459,11 +3516,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3481,11 +3538,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3503,11 +3560,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3525,11 +3582,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3547,11 +3604,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3569,11 +3626,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3591,11 +3648,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3613,11 +3670,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3635,11 +3692,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3657,11 +3714,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3679,11 +3736,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3701,11 +3758,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3723,11 +3780,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3745,11 +3802,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3767,11 +3824,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3789,11 +3846,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3811,11 +3868,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3833,11 +3890,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3855,11 +3912,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3877,11 +3934,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3899,11 +3956,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -3921,11 +3978,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -3943,11 +4000,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -3965,11 +4022,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -3987,11 +4044,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4009,11 +4066,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="16">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="17">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4031,11 +4088,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4053,11 +4110,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4075,11 +4132,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4097,11 +4154,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4119,11 +4176,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4141,11 +4198,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4163,11 +4220,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4185,11 +4242,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4207,11 +4264,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4229,11 +4286,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4251,11 +4308,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4273,11 +4330,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4295,11 +4352,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4317,11 +4374,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4339,11 +4396,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4361,11 +4418,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4383,11 +4440,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4405,11 +4462,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4427,11 +4484,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4449,11 +4506,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4471,11 +4528,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4493,11 +4550,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4515,11 +4572,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4537,11 +4594,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4559,11 +4616,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4581,11 +4638,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4603,11 +4660,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4625,11 +4682,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4647,11 +4704,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4669,11 +4726,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4691,11 +4748,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4713,11 +4770,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4735,11 +4792,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4757,11 +4814,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4779,11 +4836,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4801,11 +4858,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4823,11 +4880,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4845,11 +4902,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4867,11 +4924,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4889,11 +4946,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4911,11 +4968,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -4933,11 +4990,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -4955,11 +5012,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -4977,11 +5034,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -4999,11 +5056,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5021,11 +5078,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5043,11 +5100,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5065,11 +5122,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5087,11 +5144,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5109,11 +5166,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5131,11 +5188,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5153,11 +5210,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5175,11 +5232,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5197,11 +5254,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5219,11 +5276,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5241,11 +5298,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5263,11 +5320,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5285,11 +5342,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5307,11 +5364,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5329,11 +5386,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5351,11 +5408,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5373,11 +5430,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5395,11 +5452,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5417,11 +5474,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="18">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="19">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5439,11 +5496,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5461,11 +5518,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5483,11 +5540,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5505,11 +5562,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5527,11 +5584,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5549,11 +5606,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5571,11 +5628,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5593,11 +5650,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5615,11 +5672,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5637,11 +5694,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5659,11 +5716,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5681,11 +5738,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5703,11 +5760,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5725,11 +5782,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5747,11 +5804,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5769,11 +5826,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5791,11 +5848,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5813,11 +5870,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5835,11 +5892,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5857,11 +5914,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5879,11 +5936,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5901,11 +5958,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -5923,11 +5980,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -5945,11 +6002,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -5967,11 +6024,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -5989,11 +6046,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6011,11 +6068,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6033,11 +6090,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6055,11 +6112,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6077,11 +6134,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6099,11 +6156,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6121,11 +6178,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6143,11 +6200,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6165,11 +6222,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6187,11 +6244,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6209,11 +6266,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6231,11 +6288,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6253,11 +6310,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6275,11 +6332,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6297,11 +6354,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6319,11 +6376,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6341,11 +6398,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6363,11 +6420,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6385,11 +6442,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6407,11 +6464,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6429,11 +6486,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6451,11 +6508,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6473,11 +6530,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6495,11 +6552,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6517,11 +6574,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6539,11 +6596,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6561,11 +6618,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6583,11 +6640,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6605,11 +6662,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6627,11 +6684,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6649,11 +6706,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6671,11 +6728,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6693,11 +6750,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6715,11 +6772,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6737,11 +6794,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6759,11 +6816,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6781,11 +6838,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6803,11 +6860,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6825,11 +6882,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="20">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="21">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6847,11 +6904,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6869,11 +6926,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6891,11 +6948,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6913,11 +6970,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -6935,11 +6992,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -6957,11 +7014,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -6979,11 +7036,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7001,11 +7058,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7023,11 +7080,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7045,11 +7102,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7067,11 +7124,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7089,11 +7146,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7111,11 +7168,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7133,11 +7190,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7155,11 +7212,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7177,11 +7234,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7199,11 +7256,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7221,11 +7278,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7243,11 +7300,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7265,11 +7322,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7287,11 +7344,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7309,11 +7366,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7331,11 +7388,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7353,11 +7410,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7375,11 +7432,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7397,11 +7454,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7419,11 +7476,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7441,11 +7498,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7463,11 +7520,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7485,11 +7542,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7507,11 +7564,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7529,11 +7586,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7551,11 +7608,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7573,11 +7630,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7595,11 +7652,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7617,11 +7674,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7639,11 +7696,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7661,11 +7718,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7683,11 +7740,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7705,11 +7762,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7727,11 +7784,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7749,11 +7806,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7771,11 +7828,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7793,11 +7850,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7815,11 +7872,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7837,11 +7894,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7859,11 +7916,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7881,11 +7938,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7903,11 +7960,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -7925,11 +7982,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -7947,11 +8004,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -7969,11 +8026,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -7991,11 +8048,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8013,11 +8070,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8035,11 +8092,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8057,11 +8114,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8079,11 +8136,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8101,11 +8158,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8123,11 +8180,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8145,11 +8202,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8167,11 +8224,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8189,11 +8246,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8211,11 +8268,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8233,11 +8290,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="22">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="23">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8255,11 +8312,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8277,11 +8334,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8299,11 +8356,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8321,11 +8378,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8343,11 +8400,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8365,11 +8422,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8387,11 +8444,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8409,11 +8466,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8431,11 +8488,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8453,11 +8510,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8475,11 +8532,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8497,11 +8554,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8519,11 +8576,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8541,11 +8598,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8563,11 +8620,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8585,11 +8642,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8607,11 +8664,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8629,11 +8686,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8651,11 +8708,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8673,11 +8730,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8695,11 +8752,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8717,11 +8774,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8739,11 +8796,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8761,11 +8818,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8783,11 +8840,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8805,11 +8862,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8827,11 +8884,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8849,11 +8906,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8871,11 +8928,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8893,11 +8950,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -8915,11 +8972,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -8937,11 +8994,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -8959,11 +9016,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -8981,11 +9038,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9003,11 +9060,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9025,11 +9082,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9047,11 +9104,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9069,11 +9126,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9091,11 +9148,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9113,11 +9170,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9135,11 +9192,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9157,11 +9214,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9179,11 +9236,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9201,11 +9258,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9223,11 +9280,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9245,11 +9302,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9267,11 +9324,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9289,11 +9346,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9311,11 +9368,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9333,11 +9390,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9355,11 +9412,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9377,11 +9434,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9399,11 +9456,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9421,11 +9478,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9443,11 +9500,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9465,11 +9522,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9487,11 +9544,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9509,11 +9566,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9531,11 +9588,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9553,11 +9610,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9575,11 +9632,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9597,11 +9654,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9619,11 +9676,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9641,11 +9698,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I453" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I453" si="24">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J453" si="21">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J453" si="25">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9663,11 +9720,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9685,11 +9742,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9707,11 +9764,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9729,11 +9786,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9751,11 +9808,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9773,11 +9830,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9795,11 +9852,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9817,11 +9874,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9839,11 +9896,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9861,11 +9918,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9883,11 +9940,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12600415.xlsx
+++ b/12600415.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D44F80E2-2BA9-4481-853E-A0602D629EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27840704-0350-4A38-84EE-DB079C16215B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,15 @@
   <si>
     <t>Revised Vocab.</t>
   </si>
+  <si>
+    <t>Done vibe coding</t>
+  </si>
+  <si>
+    <t>Revised what taught in the class.</t>
+  </si>
+  <si>
+    <t>Solved a problem statement of python: Medical Diagnostic Rule System using Functions</t>
+  </si>
 </sst>
 </file>
 
@@ -253,7 +262,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +343,12 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -382,7 +397,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -426,6 +441,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1429,60 +1445,108 @@
         <v>65</v>
       </c>
       <c r="L14" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="30.75">
+      <c r="A15" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B15" s="14">
+        <v>360</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>150</v>
+      </c>
+      <c r="E15" s="14">
+        <v>20</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>300</v>
+      </c>
+      <c r="H15" s="14">
+        <v>100</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="1"/>
+        <v>510</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15">
+      <c r="A16" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>180</v>
+      </c>
+      <c r="E16" s="14">
         <v>60</v>
       </c>
-      <c r="M14" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="F16" s="14">
+        <v>400</v>
+      </c>
+      <c r="G16" s="14">
+        <v>400</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14">
+        <v>320</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15">
       <c r="A17" s="13"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
